--- a/data/信用债发行汇总_2026-08-20.xlsx
+++ b/data/信用债发行汇总_2026-08-20.xlsx
@@ -1001,7 +1001,9 @@
           <t>1.70 ~ 1.98</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>1.94</v>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>国耀融汇融资租赁有限公司</t>
@@ -1181,7 +1183,9 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="3" t="n">
+        <v>1.95</v>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>重庆市涪陵国有资产投资经营集团有限公司</t>
@@ -1353,7 +1357,9 @@
           <t>1.80 ~ 2.60</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="3" t="n">
+        <v>2.11</v>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>达州市投资有限公司</t>
@@ -1531,7 +1537,9 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>2.24</v>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>重庆市涪陵国有资产投资经营集团有限公司</t>
@@ -1707,7 +1715,9 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="3" t="n">
+        <v>1.95</v>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>武汉开发投资有限公司</t>
